--- a/Guidewire_Test Data.xlsx
+++ b/Guidewire_Test Data.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29318"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{09B8F159-9CA3-4DB4-A8E7-1F684D76A7F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5625631F-A2B6-4E93-8CF6-BD9A18FFA8A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>Username</t>
   </si>
@@ -123,6 +123,12 @@
     <t>SmartCommPwd</t>
   </si>
   <si>
+    <t>GLCompanyName</t>
+  </si>
+  <si>
+    <t>GLOfferingSelection</t>
+  </si>
+  <si>
     <t>su</t>
   </si>
   <si>
@@ -144,7 +150,7 @@
     <t>Billing</t>
   </si>
   <si>
-    <t>enigma</t>
+    <t>Enigma Fire &amp; Casualty</t>
   </si>
   <si>
     <t>ProducerCode:1</t>
@@ -202,6 +208,12 @@
   </si>
   <si>
     <t>8ONjX3ggx5RmoBbvnoZOyw==</t>
+  </si>
+  <si>
+    <t>Katalon Automation_GL_</t>
+  </si>
+  <si>
+    <t>GL Standard</t>
   </si>
 </sst>
 </file>
@@ -595,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:AF2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.28515625" style="1" customWidth="1"/>
@@ -616,7 +628,7 @@
     <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="43.5">
+    <row r="1" spans="1:32" ht="43.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -707,97 +719,109 @@
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="2" spans="1:30" ht="57.75">
+    <row r="2" spans="1:32" ht="57.75">
       <c r="A2" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G2" s="1">
         <v>78405</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="V2" s="1">
         <v>56349838</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AB2" s="1">
         <v>50000</v>
       </c>
       <c r="AC2" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/Guidewire_Test Data.xlsx
+++ b/Guidewire_Test Data.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29318"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29421"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5625631F-A2B6-4E93-8CF6-BD9A18FFA8A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5BAE7952-43D1-4C52-95FA-AFDD8D19CDCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,12 +31,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>Username</t>
   </si>
   <si>
     <t>Password</t>
+  </si>
+  <si>
+    <t>PolicyNumber</t>
   </si>
   <si>
     <t>CACompanyName</t>
@@ -607,28 +610,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF2"/>
+  <dimension ref="A1:AG2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" style="1" customWidth="1"/>
-    <col min="4" max="5" width="16.85546875" style="1" customWidth="1"/>
-    <col min="6" max="7" width="9.5703125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17.85546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="16.28515625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.28515625" style="1" customWidth="1"/>
-    <col min="12" max="14" width="9.140625" style="1"/>
-    <col min="15" max="15" width="13.85546875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="9.140625" style="1"/>
-    <col min="17" max="17" width="10" style="1" customWidth="1"/>
-    <col min="18" max="24" width="9.140625" style="1"/>
-    <col min="25" max="25" width="11.42578125" style="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="2" max="3" width="13" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" style="1" customWidth="1"/>
+    <col min="5" max="6" width="16.85546875" style="1" customWidth="1"/>
+    <col min="7" max="8" width="9.5703125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.85546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="16.28515625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="17.28515625" style="1" customWidth="1"/>
+    <col min="13" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="13.85546875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.140625" style="1"/>
+    <col min="18" max="18" width="10" style="1" customWidth="1"/>
+    <col min="19" max="25" width="9.140625" style="1"/>
+    <col min="26" max="26" width="11.42578125" style="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="43.5">
+    <row r="1" spans="1:33" ht="43.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -725,16 +728,19 @@
       <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="2" spans="1:32" ht="57.75">
+    <row r="2" spans="1:33" ht="57.75">
       <c r="A2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="1" t="s">
         <v>34</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2406488048</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>35</v>
@@ -745,11 +751,11 @@
       <c r="F2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" s="1">
         <v>78405</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>39</v>
@@ -772,13 +778,13 @@
       <c r="O2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="1" t="s">
         <v>46</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R2" s="2" t="s">
         <v>48</v>
       </c>
       <c r="S2" s="1" t="s">
@@ -787,14 +793,14 @@
       <c r="T2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="U2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="V2" s="1">
+      <c r="V2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="W2" s="1">
         <v>56349838</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="X2" s="1" t="s">
         <v>53</v>
@@ -802,19 +808,19 @@
       <c r="Y2" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="Z2" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AA2" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="AB2" s="1">
+      <c r="AB2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC2" s="1">
         <v>50000</v>
       </c>
-      <c r="AC2" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AD2" s="4" t="s">
         <v>58</v>
       </c>
       <c r="AE2" s="1" t="s">
@@ -822,11 +828,14 @@
       </c>
       <c r="AF2" s="1" t="s">
         <v>60</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="AC2" r:id="rId1" xr:uid="{FEC4C7EE-A152-49B5-8CBF-2441ACC3692A}"/>
+    <hyperlink ref="AD2" r:id="rId1" xr:uid="{FEC4C7EE-A152-49B5-8CBF-2441ACC3692A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
